--- a/data/trans_orig/Q24D_2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q24D_2-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de veces que han intentado dejar de fumar</t>
+          <t>Número medio de veces que han intentado dejar de fumar (tasa de respuesta: 91,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,66; 4,21</t>
+          <t>2,71; 4,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 3,12</t>
+          <t>2,36; 3,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 2,77</t>
+          <t>2,06; 2,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 4,93</t>
+          <t>2,52; 5,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,54</t>
+          <t>1,8; 2,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 2,44</t>
+          <t>1,85; 2,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 3,36</t>
+          <t>2,32; 3,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 4,04</t>
+          <t>2,5; 3,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 3,8</t>
+          <t>2,52; 3,67</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 2,69</t>
+          <t>2,23; 2,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 2,87</t>
+          <t>2,27; 2,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 4,19</t>
+          <t>2,68; 4,22</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 3,45</t>
+          <t>2,32; 3,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,47; 3,28</t>
+          <t>2,46; 3,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 2,77</t>
+          <t>2,35; 2,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,22</t>
+          <t>2,37; 4,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 2,44</t>
+          <t>2,01; 2,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 2,84</t>
+          <t>2,32; 2,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 2,62</t>
+          <t>2,21; 2,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 3,18</t>
+          <t>2,48; 3,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 2,84</t>
+          <t>2,22; 2,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,47; 2,93</t>
+          <t>2,47; 2,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 2,62</t>
+          <t>2,32; 2,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 3,42</t>
+          <t>2,54; 3,4</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 2,87</t>
+          <t>1,86; 2,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 2,96</t>
+          <t>2,17; 2,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,03</t>
+          <t>2,22; 3,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 3,79</t>
+          <t>2,44; 3,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,99</t>
+          <t>1,8; 2,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,04</t>
+          <t>2,09; 3,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,46</t>
+          <t>1,84; 3,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 2,97</t>
+          <t>2,12; 3,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 2,75</t>
+          <t>1,89; 2,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 2,83</t>
+          <t>2,23; 2,84</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,38</t>
+          <t>2,1; 3,38</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 3,26</t>
+          <t>2,41; 3,24</t>
         </is>
       </c>
     </row>
@@ -1136,27 +1136,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 3,27</t>
+          <t>2,51; 3,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,5; 3,04</t>
+          <t>2,51; 3,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 2,77</t>
+          <t>2,37; 2,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,59; 3,75</t>
+          <t>2,57; 3,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 2,37</t>
+          <t>2,04; 2,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1166,32 +1166,32 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 2,64</t>
+          <t>2,26; 2,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 3,11</t>
+          <t>2,53; 3,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 2,82</t>
+          <t>2,33; 2,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 2,77</t>
+          <t>2,43; 2,76</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 2,64</t>
+          <t>2,37; 2,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,63; 3,25</t>
+          <t>2,64; 3,32</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q24D_2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q24D_2-Estudios-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,44</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,24</t>
+          <t>3,29</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,22</t>
+          <t>2,7; 4,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 3,1</t>
+          <t>2,37; 3,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 2,78</t>
+          <t>2,06; 2,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,03</t>
+          <t>2,56; 5,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,57</t>
+          <t>1,85; 2,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 2,45</t>
+          <t>1,84; 2,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 3,45</t>
+          <t>2,33; 3,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 3,98</t>
+          <t>2,49; 3,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 3,67</t>
+          <t>2,51; 3,73</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 2,71</t>
+          <t>2,24; 2,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 2,86</t>
+          <t>2,26; 2,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,68; 4,22</t>
+          <t>2,73; 4,19</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,82</t>
+          <t>3,13</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,79</t>
+          <t>2,8</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,8</t>
+          <t>2,97</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 3,42</t>
+          <t>2,3; 3,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 3,23</t>
+          <t>2,46; 3,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 2,82</t>
+          <t>2,33; 2,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 4,26</t>
+          <t>2,55; 4,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 2,43</t>
+          <t>2,0; 2,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 2,81</t>
+          <t>2,33; 2,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 2,61</t>
+          <t>2,21; 2,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 3,2</t>
+          <t>2,46; 3,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 2,84</t>
+          <t>2,21; 2,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,47; 2,92</t>
+          <t>2,46; 2,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 2,64</t>
+          <t>2,32; 2,63</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 3,4</t>
+          <t>2,67; 3,58</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,95</t>
+          <t>2,86</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,48</t>
+          <t>2,63</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,74</t>
+          <t>2,75</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 2,88</t>
+          <t>1,88; 2,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 2,97</t>
+          <t>2,19; 3,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,99</t>
+          <t>2,21; 4,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 3,82</t>
+          <t>2,34; 3,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,91</t>
+          <t>1,75; 2,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,01</t>
+          <t>2,1; 3,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,31</t>
+          <t>1,82; 3,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,0</t>
+          <t>2,23; 3,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 2,64</t>
+          <t>1,95; 2,71</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 2,84</t>
+          <t>2,22; 2,82</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,38</t>
+          <t>2,12; 3,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 3,24</t>
+          <t>2,44; 3,22</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,94</t>
+          <t>3,16</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,78</t>
+          <t>2,81</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,86</t>
+          <t>2,99</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 3,25</t>
+          <t>2,51; 3,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 3,02</t>
+          <t>2,52; 3,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 2,76</t>
+          <t>2,37; 2,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,57; 3,7</t>
+          <t>2,73; 3,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 2,39</t>
+          <t>2,03; 2,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 2,63</t>
+          <t>2,29; 2,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 2,64</t>
+          <t>2,27; 2,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 3,12</t>
+          <t>2,55; 3,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 2,8</t>
+          <t>2,35; 2,83</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 2,76</t>
+          <t>2,45; 2,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 2,64</t>
+          <t>2,37; 2,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,64; 3,32</t>
+          <t>2,75; 3,48</t>
         </is>
       </c>
     </row>
